--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_189_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_189_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0186</v>
+        <v>4.7662</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0725</v>
+        <v>4.9546</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0539</v>
+        <v>-0.1884</v>
       </c>
       <c r="G2" t="n">
         <v>1.7452</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>1.361</v>
+        <v>1.1086</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6449</v>
+        <v>0.5269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7161</v>
+        <v>0.5816</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5148</v>
+        <v>3.5554</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9472</v>
+        <v>3.3575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5676</v>
+        <v>0.1979</v>
       </c>
       <c r="G3" t="n">
         <v>2.1668</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1161</v>
+        <v>1.1567</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2819</v>
+        <v>0.6921</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.4646</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3311</v>
+        <v>3.163</v>
       </c>
       <c r="E4" t="n">
         <v>2.5327</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7983</v>
+        <v>0.6303</v>
       </c>
       <c r="G4" t="n">
         <v>3.1756</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2183</v>
+        <v>-0.3864</v>
       </c>
       <c r="T4" t="n">
         <v>-0.4402</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2219</v>
+        <v>0.0538</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8756</v>
+        <v>2.8523</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8647</v>
+        <v>4.015</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9891</v>
+        <v>-1.1626</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2071</v>
+        <v>0.7402</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8366</v>
+        <v>0.0143</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6295</v>
+        <v>0.7259</v>
       </c>
       <c r="J5" t="n">
-        <v>2.39</v>
+        <v>0.9371</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4402</v>
+        <v>-0.0029</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0502</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1829</v>
+        <v>-0.1969</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3963</v>
+        <v>0.0171</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5792</v>
+        <v>-0.214</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2921</v>
+        <v>0.0246</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5623</v>
+        <v>0.3973</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2702</v>
+        <v>-0.3727</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6462</v>
+        <v>2.5319</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6873</v>
+        <v>3.2186</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0411</v>
+        <v>-0.6867</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0583</v>
+        <v>1.2071</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7008</v>
+        <v>2.8366</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6425</v>
+        <v>-1.6295</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8125</v>
+        <v>2.39</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1903</v>
+        <v>2.4402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6222</v>
+        <v>-0.0502</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7542</v>
+        <v>-1.1829</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5105</v>
+        <v>0.3963</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2647</v>
+        <v>-1.5792</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1801</v>
+        <v>0.9484</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1098</v>
+        <v>0.9162</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0703</v>
+        <v>0.0323</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2045</v>
+        <v>2.4868</v>
       </c>
       <c r="E7" t="n">
-        <v>2.804</v>
+        <v>3.6623</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5995</v>
+        <v>-1.1755</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7402</v>
+        <v>1.0583</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0143</v>
+        <v>1.7008</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7259</v>
+        <v>-0.6425</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9371</v>
+        <v>1.8125</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0029</v>
+        <v>1.1903</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6222</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1969</v>
+        <v>-0.7542</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0171</v>
+        <v>0.5105</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.214</v>
+        <v>-1.2647</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6232</v>
+        <v>0.6605</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8136</v>
+        <v>0.8652</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8096</v>
+        <v>-0.2047</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6805</v>
+        <v>2.1444</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6805</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9563</v>
+        <v>0.365</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7858</v>
+        <v>1.4634</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8295</v>
+        <v>-1.0983</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9365</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2871</v>
+        <v>0.6959</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7591</v>
+        <v>0.4367</v>
       </c>
       <c r="U8" t="n">
-        <v>0.528</v>
+        <v>0.2592</v>
       </c>
       <c r="V8" t="n">
         <v>0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2485</v>
+        <v>-0.0319</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9237</v>
+        <v>2.0731</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1722</v>
+        <v>-2.105</v>
       </c>
       <c r="G9" t="n">
         <v>0.4407</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0808</v>
+        <v>0.1357</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1889</v>
+        <v>0.3383</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0361</v>
+        <v>-1.4407</v>
       </c>
       <c r="E10" t="n">
-        <v>0.749</v>
+        <v>0.2772</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7851</v>
+        <v>-1.7178</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6328</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7565</v>
+        <v>0.3519</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7117</v>
+        <v>0.2399</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3368</v>
+        <v>-2.2889</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1215</v>
+        <v>-1.208</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2153</v>
+        <v>-1.0809</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4684</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1316</v>
+        <v>1.1795</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1993</v>
+        <v>1.1127</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.473</v>
+        <v>-2.7596</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2683</v>
+        <v>0.9145</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7413</v>
+        <v>-3.6741</v>
       </c>
       <c r="G12" t="n">
         <v>1.3713</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3697</v>
+        <v>1.0831</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4233</v>
+        <v>1.0695</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0536</v>
+        <v>0.0136</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3584</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.4527</v>
+        <v>13.1995</v>
       </c>
       <c r="E13" t="n">
-        <v>24.5137</v>
+        <v>25.2609</v>
       </c>
       <c r="F13" t="n">
         <v>-12.0611</v>
       </c>
       <c r="G13" t="n">
-        <v>8.8675</v>
+        <v>8.867500000000001</v>
       </c>
       <c r="H13" t="n">
         <v>10.7076</v>
@@ -1468,13 +1468,13 @@
         <v>10.4379</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2117</v>
+        <v>6.958499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>5.4078</v>
+        <v>6.154599999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8039000000000001</v>
+        <v>0.8039999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4665</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7148</v>
+        <v>1.782</v>
       </c>
       <c r="E14" t="n">
         <v>2.4794</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.6974</v>
       </c>
       <c r="G14" t="n">
         <v>0.8038999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.107</v>
+        <v>-1.0398</v>
       </c>
       <c r="T14" t="n">
         <v>-0.5228</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5843</v>
+        <v>-0.5171</v>
       </c>
       <c r="V14" t="n">
         <v>0.3943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6807</v>
+        <v>0.9223</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3313</v>
+        <v>2.4493</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6506</v>
+        <v>-1.527</v>
       </c>
       <c r="G15" t="n">
         <v>-1.013</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2034</v>
+        <v>0.0382</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1336</v>
+        <v>-0.0156</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0698</v>
+        <v>0.0538</v>
       </c>
       <c r="V15" t="n">
         <v>3.7527</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0127</v>
+        <v>0.6836</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6491</v>
+        <v>4.121</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.6618</v>
+        <v>-3.4373</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5728</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2801</v>
+        <v>-0.5838</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6484</v>
+        <v>-0.1766</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6317</v>
+        <v>-0.4072</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2309</v>
+        <v>0.1788</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0786</v>
+        <v>1.1966</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3095</v>
+        <v>-1.0178</v>
       </c>
       <c r="G17" t="n">
         <v>2.6978</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0884</v>
+        <v>-1.6788</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9709</v>
+        <v>-0.8529</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1176</v>
+        <v>-0.8259</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5396</v>
+        <v>-0.506</v>
       </c>
       <c r="E18" t="n">
         <v>-0.7749</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2353</v>
+        <v>0.2689</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3404</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.127</v>
+        <v>-0.0934</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3779</v>
+        <v>-1.2421</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8425</v>
+        <v>1.3143</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2204</v>
+        <v>-2.5565</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2899</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9436</v>
+        <v>-0.8079</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2047</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3178</v>
+        <v>-1.8245</v>
       </c>
       <c r="E20" t="n">
         <v>2.573</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.8908</v>
+        <v>-4.3975</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3028</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7651</v>
+        <v>-1.2718</v>
       </c>
       <c r="T20" t="n">
         <v>0.0633</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8284</v>
+        <v>-1.335</v>
       </c>
       <c r="V20" t="n">
         <v>0.6778999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9249</v>
+        <v>-3.3124</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4618</v>
+        <v>0.108</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3867</v>
+        <v>-3.4203</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9129</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6357</v>
+        <v>-1.0231</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2715</v>
+        <v>-0.0824</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9071</v>
+        <v>-0.9408</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6083</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3931</v>
+        <v>-4.0958</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6844</v>
+        <v>0.5684</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7087</v>
+        <v>-4.6642</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.7114</v>
+        <v>-1.2258</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6469</v>
+        <v>-0.5834</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0645</v>
+        <v>-0.6424</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1878</v>
+        <v>1.3662</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4383</v>
+        <v>0.9011</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.465</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5236</v>
+        <v>-2.592</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2087</v>
+        <v>-1.4845</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3149</v>
+        <v>-1.1074</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>2.0142</v>
+        <v>-0.1199</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6632</v>
+        <v>0.362</v>
       </c>
       <c r="U22" t="n">
-        <v>0.351</v>
+        <v>-0.4819</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0514</v>
+        <v>-4.2523</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5684</v>
+        <v>-2.51</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6198</v>
+        <v>-1.7423</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2258</v>
+        <v>-4.7114</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5834</v>
+        <v>-2.6469</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6424</v>
+        <v>-2.0645</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3662</v>
+        <v>-2.1878</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9011</v>
+        <v>-1.4383</v>
       </c>
       <c r="L23" t="n">
-        <v>0.465</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.592</v>
+        <v>-2.5236</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4845</v>
+        <v>-1.2087</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1074</v>
+        <v>-1.3149</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0756</v>
+        <v>1.1549</v>
       </c>
       <c r="T23" t="n">
-        <v>0.362</v>
+        <v>0.8375</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4375</v>
+        <v>0.3174</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.4528</v>
+        <v>-11.6664</v>
       </c>
       <c r="E24" t="n">
-        <v>11.5248</v>
+        <v>11.5251</v>
       </c>
       <c r="F24" t="n">
-        <v>-23.9776</v>
+        <v>-23.1914</v>
       </c>
       <c r="G24" t="n">
         <v>-8.8673</v>
@@ -2326,13 +2326,13 @@
         <v>11.5976</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.2117</v>
+        <v>-5.4254</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8040000000000002</v>
+        <v>-0.8039999999999997</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.4077</v>
+        <v>-4.6215</v>
       </c>
       <c r="V24" t="n">
         <v>1.4665</v>
